--- a/jira_export_2026-07-27.xlsx
+++ b/jira_export_2026-07-27.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>56,043 €</t>
+          <t>56,242 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -763,7 +763,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>20,014 €</t>
+          <t>20,214 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>493 h</t>
+          <t>495 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>865.15</v>
+        <v>1064.8</v>
       </c>
       <c r="P40" s="15" t="n">
-        <v>84.40000000000001</v>
+        <v>103.88</v>
       </c>
     </row>
     <row r="41">
@@ -13610,10 +13610,10 @@
         <v>65939.26000000001</v>
       </c>
       <c r="O185" s="18" t="n">
-        <v>56042.565</v>
+        <v>56242.215</v>
       </c>
       <c r="P185" s="18" t="n">
-        <v>179.19</v>
+        <v>179.83</v>
       </c>
     </row>
   </sheetData>
@@ -13810,7 +13810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -13836,7 +13836,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 7 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 8 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -13954,22 +13954,22 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
+          <t>[COMMUNE DE FRONTON] - Simple commande de Pax pour installer Placier dessus</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Achat nouveau PAX A920</t>
+          <t>Simple commande de Pax pour installer Placier dessus</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -13992,12 +13992,12 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34343</t>
+          <t>PDMDEP-34525</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>00171709</t>
+          <t>00173006</t>
         </is>
       </c>
       <c r="K6" s="15" t="n">
@@ -14007,22 +14007,22 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H7" s="11" t="n">
@@ -14045,37 +14045,37 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34214</t>
+          <t>PDMDEP-34343</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171709</t>
         </is>
       </c>
       <c r="K7" s="12" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34147</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en place de deux PAX</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Vaison la romaine</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'une régie et mise en place de deux PAX</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H8" s="14" t="n">
@@ -14098,37 +14098,37 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34153</t>
+          <t>PDMDEP-34214</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>00171079</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="K8" s="15" t="n">
-        <v>1630</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33755</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
+          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en place de deux PAX</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MAINTENON</t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Ajout d'une régie et mise en place de deux PAX</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H9" s="11" t="n">
@@ -14151,37 +14151,37 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33762</t>
+          <t>PDMDEP-34153</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>00169559</t>
+          <t>00171079</t>
         </is>
       </c>
       <c r="K9" s="12" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-33755</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DE MAINTENON</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H10" s="14" t="n">
@@ -14204,12 +14204,12 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32739</t>
+          <t>PDMDEP-33762</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>00163790</t>
+          <t>00169559</t>
         </is>
       </c>
       <c r="K10" s="15" t="n">
@@ -14219,73 +14219,126 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
+          <t>PDMDEP-32732</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LA SENTINELLE</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Acquisition Geodp Caisse</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32739</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>00163790</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
           <t>PDMDEP-32152</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="H11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-32159</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>00160662</t>
         </is>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="K12" s="15" t="n">
         <v>1711.5</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr"/>
-      <c r="C12" s="17" t="inlineStr"/>
-      <c r="D12" s="17" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr"/>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr"/>
-      <c r="H12" s="17" t="inlineStr"/>
-      <c r="I12" s="17" t="inlineStr"/>
-      <c r="J12" s="17" t="inlineStr"/>
-      <c r="K12" s="18" t="n">
-        <v>7416.5</v>
+      <c r="B13" s="17" t="inlineStr"/>
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="17" t="inlineStr"/>
+      <c r="E13" s="17" t="inlineStr"/>
+      <c r="F13" s="17" t="inlineStr"/>
+      <c r="G13" s="17" t="inlineStr"/>
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
+      <c r="J13" s="17" t="inlineStr"/>
+      <c r="K13" s="18" t="n">
+        <v>8231.5</v>
       </c>
     </row>
   </sheetData>
@@ -14298,6 +14351,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14784,7 +14838,7 @@
         <v>206.5</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>486.15</v>
@@ -14833,7 +14887,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>104.33</v>
+        <v>105.83</v>
       </c>
     </row>
   </sheetData>
@@ -14918,10 +14972,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>384733</v>
+        <v>384533</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>112947</v>
+        <v>112747</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>271786</v>
@@ -14943,10 +14997,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>175691</v>
+        <v>175491</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>64508</v>
+        <v>64308</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>111183</v>
@@ -14997,7 +15051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15021,7 +15075,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 17 commande(s)</t>
+          <t>Épics créées ce mois — 16 commande(s)</t>
         </is>
       </c>
     </row>
@@ -15076,22 +15130,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34751</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34745</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>VILLE D'OLONZAC</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -15101,7 +15155,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -15111,32 +15165,32 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00176937</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>0</v>
+        <v>3947.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -15156,32 +15210,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>4475</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -15201,32 +15255,32 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>1050</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34527</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34521</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE FRONTON</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -15236,7 +15290,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -15246,32 +15300,32 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00173007</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>500</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34545</t>
+          <t>PDMDEP-34621</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34537</t>
+          <t>PDMDEP-34613</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRON</t>
+          <t>COMMUNE DE FORT-DE-FRANCE</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -15291,44 +15345,44 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00173172</t>
+          <t>00176431</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34566</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34559</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
+          <t>COMMUNE DE RIEZ</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Services</t>
@@ -15336,32 +15390,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00154892</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>5000</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34566</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34559</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -15381,32 +15435,32 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00154892</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>2035</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34545</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34537</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE BRON</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -15416,7 +15470,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -15426,32 +15480,32 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00173172</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34527</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -15461,7 +15515,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -15471,32 +15525,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00173007</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>2250</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34666</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34659</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -15516,32 +15570,32 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>2000</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34683</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34676</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -15561,32 +15615,32 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>2150</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -15606,32 +15660,32 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>3947.5</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34621</t>
+          <t>PDMDEP-34396</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34613</t>
+          <t>PDMDEP-34390</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE FORT-DE-FRANCE</t>
+          <t>Commune Le THOR</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -15651,37 +15705,37 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>00176431</t>
+          <t>00171793</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34396</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34390</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Commune Le THOR</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -15696,11 +15750,11 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>00171793</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>250</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="19">
@@ -15794,54 +15848,30 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34722</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34718</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>24/07/2026</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>VILLE DE VILLEURBANNE</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>00176875</t>
-        </is>
-      </c>
-      <c r="I21" s="25" t="n">
-        <v>2800</v>
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>16 commande(s)</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="n">
+        <v>35552</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B22" s="17" t="n"/>
@@ -15852,17 +15882,17 @@
       <c r="G22" s="17" t="n"/>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>17 commande(s)</t>
+          <t>3 commande(s)</t>
         </is>
       </c>
       <c r="I22" s="24" t="n">
-        <v>35552</v>
+        <v>7595</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>dont GEODP</t>
         </is>
       </c>
       <c r="B23" s="17" t="n"/>
@@ -15873,31 +15903,10 @@
       <c r="G23" s="17" t="n"/>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>3 commande(s)</t>
+          <t>13 commande(s)</t>
         </is>
       </c>
       <c r="I23" s="24" t="n">
-        <v>7595</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>dont GEODP</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>14 commande(s)</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="n">
         <v>27958</v>
       </c>
     </row>
